--- a/filesystem/Legal/Reyes/docket_entry.xlsx
+++ b/filesystem/Legal/Reyes/docket_entry.xlsx
@@ -140,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -197,11 +197,29 @@
         <color rgb="FFD5DBE2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD5DBE2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFB08D57"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -255,6 +273,8 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,6 +604,16 @@
           <t>Halstead &amp; Cruz LLP — Matter Deadline Docket Entry</t>
         </is>
       </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+      <c r="K1" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -668,15 +698,15 @@
           <t>Attorneys of record and paralegal team only</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="20" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
